--- a/outputs/model_results/MCLR/Model 2_beta_coef.xlsx
+++ b/outputs/model_results/MCLR/Model 2_beta_coef.xlsx
@@ -471,29 +471,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.311</t>
+          <t>-0.296</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.193</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.0038</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3573</v>
+        <v>4251</v>
       </c>
       <c r="G2" t="n">
-        <v>1968</v>
+        <v>2774</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -502,12 +502,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0035</t>
+          <t>0.0024</t>
         </is>
       </c>
     </row>
@@ -519,29 +519,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3035</v>
+        <v>3847</v>
       </c>
       <c r="G3" t="n">
-        <v>2405</v>
+        <v>2686</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -550,12 +550,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.0099</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0078</t>
+          <t>0.0072</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -582,14 +582,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3081</v>
+        <v>3934</v>
       </c>
       <c r="G4" t="n">
-        <v>2703</v>
+        <v>2889</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -598,12 +598,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.0096</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0078</t>
+          <t>0.0069</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5277</v>
+        <v>4910</v>
       </c>
       <c r="G5" t="n">
-        <v>3002</v>
+        <v>2912</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,12 +646,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.0084</t>
         </is>
       </c>
     </row>
@@ -663,17 +663,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4172</v>
+        <v>4045</v>
       </c>
       <c r="G6" t="n">
-        <v>2540</v>
+        <v>2524</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>0.0084</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3490</v>
+        <v>3458</v>
       </c>
       <c r="G7" t="n">
-        <v>2535</v>
+        <v>2993</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0087</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -759,29 +759,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3350</v>
+        <v>3312</v>
       </c>
       <c r="G8" t="n">
-        <v>2599</v>
+        <v>2778</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -812,24 +812,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3365</v>
+        <v>3411</v>
       </c>
       <c r="G9" t="n">
-        <v>2683</v>
+        <v>2713</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -838,12 +838,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0094</t>
+          <t>0.0092</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0067</t>
         </is>
       </c>
     </row>
@@ -855,29 +855,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4144</v>
+        <v>4565</v>
       </c>
       <c r="G10" t="n">
-        <v>2677</v>
+        <v>2703</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -886,12 +886,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0083</t>
+          <t>0.0079</t>
         </is>
       </c>
     </row>
@@ -913,19 +913,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3250</v>
+        <v>3374</v>
       </c>
       <c r="G11" t="n">
-        <v>2904</v>
+        <v>2885</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0096</t>
+          <t>0.0094</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -956,24 +956,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3151</v>
+        <v>3415</v>
       </c>
       <c r="G12" t="n">
-        <v>2772</v>
+        <v>2655</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0098</t>
+          <t>0.0096</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1014,14 +1014,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3088</v>
+        <v>3433</v>
       </c>
       <c r="G13" t="n">
-        <v>2861</v>
+        <v>2812</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.0098</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0077</t>
+          <t>0.007</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1047,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3487</v>
+        <v>3301</v>
       </c>
       <c r="G14" t="n">
-        <v>2554</v>
+        <v>2612</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0098</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0073</t>
         </is>
       </c>
     </row>
@@ -1095,29 +1095,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="G15" t="n">
-        <v>2742</v>
+        <v>2756</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0072</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5440</v>
+        <v>5592</v>
       </c>
       <c r="G16" t="n">
-        <v>2938</v>
+        <v>3247</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.226</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1206,14 +1206,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5181</v>
+        <v>4279</v>
       </c>
       <c r="G17" t="n">
-        <v>2426</v>
+        <v>2324</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.003</t>
         </is>
       </c>
     </row>
@@ -1239,29 +1239,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>0.241</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5992</v>
+        <v>5657</v>
       </c>
       <c r="G18" t="n">
-        <v>2479</v>
+        <v>3005</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0033</t>
+          <t>0.0031</t>
         </is>
       </c>
     </row>
@@ -1287,29 +1287,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-0.227</t>
+          <t>-0.229</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6050</v>
+        <v>5113</v>
       </c>
       <c r="G19" t="n">
-        <v>2824</v>
+        <v>2131</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0035</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0033</t>
+          <t>0.003</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4948</v>
+        <v>5445</v>
       </c>
       <c r="G20" t="n">
-        <v>2439</v>
+        <v>2470</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0039</t>
+          <t>0.0037</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0039</t>
+          <t>0.0037</t>
         </is>
       </c>
     </row>
@@ -1383,29 +1383,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-0.244</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4456</v>
+        <v>4223</v>
       </c>
       <c r="G21" t="n">
-        <v>2730</v>
+        <v>2415</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0037</t>
+          <t>0.0034</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0035</t>
+          <t>0.0029</t>
         </is>
       </c>
     </row>
@@ -1431,29 +1431,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6019</v>
+        <v>5901</v>
       </c>
       <c r="G22" t="n">
-        <v>2668</v>
+        <v>2718</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0033</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0028</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5551</v>
+        <v>4809</v>
       </c>
       <c r="G23" t="n">
-        <v>3065</v>
+        <v>2523</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0035</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1527,29 +1527,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5056</v>
+        <v>5343</v>
       </c>
       <c r="G24" t="n">
-        <v>2776</v>
+        <v>2980</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0034</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0033</t>
+          <t>0.0032</t>
         </is>
       </c>
     </row>
@@ -1575,29 +1575,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.222</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4799</v>
+        <v>4657</v>
       </c>
       <c r="G25" t="n">
-        <v>2710</v>
+        <v>2684</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0033</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0038</t>
+          <t>0.0029</t>
         </is>
       </c>
     </row>
@@ -1623,29 +1623,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-0.131</t>
+          <t>-0.116</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>0.256</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3811</v>
+        <v>4061</v>
       </c>
       <c r="G26" t="n">
-        <v>2263</v>
+        <v>2597</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0046</t>
+          <t>0.0041</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0034</t>
         </is>
       </c>
     </row>
@@ -1671,29 +1671,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.251</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5733</v>
+        <v>4849</v>
       </c>
       <c r="G27" t="n">
-        <v>2585</v>
+        <v>2534</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>0.0037</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>0.0035</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.0036</t>
         </is>
       </c>
     </row>
@@ -1719,29 +1719,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-0.141</t>
+          <t>-0.149</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5632</v>
+        <v>5247</v>
       </c>
       <c r="G28" t="n">
-        <v>2807</v>
+        <v>2530</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0035</t>
+          <t>0.0037</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1767,29 +1767,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.086</t>
+          <t>-0.078</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4562</v>
+        <v>3906</v>
       </c>
       <c r="G29" t="n">
-        <v>2883</v>
+        <v>2615</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0024</t>
+          <t>0.0023</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1830,14 +1830,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3832</v>
+        <v>3973</v>
       </c>
       <c r="G30" t="n">
-        <v>2328</v>
+        <v>2796</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0041</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0042</t>
+          <t>0.0031</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-0.106</t>
+          <t>-0.103</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5195</v>
+        <v>4025</v>
       </c>
       <c r="G31" t="n">
-        <v>3013</v>
+        <v>2336</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0038</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0036</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-0.189</t>
+          <t>-0.179</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1921,23 +1921,23 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5620</v>
+        <v>5180</v>
       </c>
       <c r="G32" t="n">
-        <v>2660</v>
+        <v>2544</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0033</t>
         </is>
       </c>
     </row>
@@ -1959,29 +1959,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.215</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5259</v>
+        <v>4731</v>
       </c>
       <c r="G33" t="n">
-        <v>2372</v>
+        <v>2779</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0031</t>
+          <t>0.0028</t>
         </is>
       </c>
     </row>

--- a/outputs/model_results/MCLR/Model 2_beta_coef.xlsx
+++ b/outputs/model_results/MCLR/Model 2_beta_coef.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,34 +466,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>beta_nbr_lanes</t>
+          <t>beta_nbr_lanes[0]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.296</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.0038</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4251</v>
+        <v>2030</v>
       </c>
       <c r="G2" t="n">
-        <v>2774</v>
+        <v>2682</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -502,46 +502,46 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0024</t>
+          <t>0.0079</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>beta_type[0]</t>
+          <t>beta_nbr_lanes[1]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3847</v>
+        <v>2244</v>
       </c>
       <c r="G3" t="n">
-        <v>2686</v>
+        <v>2373</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -550,46 +550,46 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0099</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.0078</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>beta_type[1]</t>
+          <t>beta_nbr_lanes[2]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3934</v>
+        <v>2106</v>
       </c>
       <c r="G4" t="n">
-        <v>2889</v>
+        <v>2546</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -598,46 +598,46 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0096</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0084</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>beta_type[2]</t>
+          <t>beta_type[0]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4910</v>
+        <v>2460</v>
       </c>
       <c r="G5" t="n">
-        <v>2912</v>
+        <v>1975</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -646,34 +646,34 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.0063</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0084</t>
+          <t>0.0054</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>beta_type[3]</t>
+          <t>beta_type[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4045</v>
+        <v>4036</v>
       </c>
       <c r="G6" t="n">
-        <v>2524</v>
+        <v>2730</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -694,46 +694,46 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0084</t>
+          <t>0.0083</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>beta_slope[0]</t>
+          <t>beta_type[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3458</v>
+        <v>2862</v>
       </c>
       <c r="G7" t="n">
-        <v>2993</v>
+        <v>2586</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -742,46 +742,46 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0087</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0062</t>
+          <t>0.006</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>beta_slope[1]</t>
+          <t>beta_slope[0]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.428</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.041</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3312</v>
+        <v>2511</v>
       </c>
       <c r="G8" t="n">
-        <v>2778</v>
+        <v>1577</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -790,46 +790,46 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0049</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0063</t>
+          <t>0.0046</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>beta_slope[2]</t>
+          <t>beta_slope[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3411</v>
+        <v>2955</v>
       </c>
       <c r="G9" t="n">
-        <v>2713</v>
+        <v>2183</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -838,12 +838,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0067</t>
+          <t>0.0054</t>
         </is>
       </c>
     </row>
@@ -855,29 +855,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4565</v>
+        <v>2108</v>
       </c>
       <c r="G10" t="n">
-        <v>2703</v>
+        <v>2678</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0079</t>
+          <t>0.0082</t>
         </is>
       </c>
     </row>
@@ -903,29 +903,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3374</v>
+        <v>2100</v>
       </c>
       <c r="G11" t="n">
-        <v>2885</v>
+        <v>2598</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0094</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0066</t>
+          <t>0.0084</t>
         </is>
       </c>
     </row>
@@ -951,29 +951,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3415</v>
+        <v>2447</v>
       </c>
       <c r="G12" t="n">
-        <v>2655</v>
+        <v>2540</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -982,46 +982,46 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0096</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0069</t>
+          <t>0.0077</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beta_speed[3]</t>
+          <t>beta_green[0]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3433</v>
+        <v>2655</v>
       </c>
       <c r="G13" t="n">
-        <v>2812</v>
+        <v>1837</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1030,46 +1030,46 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0098</t>
+          <t>0.0056</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.0046</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>beta_green[0]</t>
+          <t>beta_green[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3301</v>
+        <v>3944</v>
       </c>
       <c r="G14" t="n">
-        <v>2612</v>
+        <v>2679</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1078,46 +1078,46 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0073</t>
+          <t>0.0088</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>beta_green[1]</t>
+          <t>v_photo[0]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3293</v>
+        <v>2194</v>
       </c>
       <c r="G15" t="n">
-        <v>2756</v>
+        <v>1709</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1126,46 +1126,46 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0072</t>
+          <t>0.0063</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>beta_green[2]</t>
+          <t>v_photo[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5592</v>
+        <v>3410</v>
       </c>
       <c r="G16" t="n">
-        <v>3247</v>
+        <v>1921</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1174,46 +1174,46 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.0052</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0074</t>
+          <t>0.0054</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>v_photo[0]</t>
+          <t>v_photo[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4279</v>
+        <v>4326</v>
       </c>
       <c r="G17" t="n">
-        <v>2324</v>
+        <v>2567</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1222,46 +1222,46 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0046</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.0049</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>v_photo[1]</t>
+          <t>v_photo[3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5657</v>
+        <v>3495</v>
       </c>
       <c r="G18" t="n">
-        <v>3005</v>
+        <v>1905</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1270,46 +1270,46 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0052</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0031</t>
+          <t>0.0052</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>v_photo[2]</t>
+          <t>v_photo[4]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-0.229</t>
+          <t>-0.226</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5113</v>
+        <v>2968</v>
       </c>
       <c r="G19" t="n">
-        <v>2131</v>
+        <v>2074</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1318,46 +1318,46 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0035</t>
+          <t>0.0048</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.0045</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>v_photo[3]</t>
+          <t>v_photo[5]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.284</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5445</v>
+        <v>4377</v>
       </c>
       <c r="G20" t="n">
-        <v>2470</v>
+        <v>2626</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1366,46 +1366,46 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0037</t>
+          <t>0.0043</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0037</t>
+          <t>0.0044</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>v_photo[4]</t>
+          <t>v_photo[6]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4223</v>
+        <v>3856</v>
       </c>
       <c r="G21" t="n">
-        <v>2415</v>
+        <v>2246</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1414,46 +1414,46 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0046</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0046</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>v_photo[5]</t>
+          <t>v_photo[7]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5901</v>
+        <v>3286</v>
       </c>
       <c r="G22" t="n">
-        <v>2718</v>
+        <v>1905</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1462,46 +1462,46 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0053</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0028</t>
+          <t>0.0054</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>v_photo[6]</t>
+          <t>v_photo[8]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4809</v>
+        <v>3086</v>
       </c>
       <c r="G23" t="n">
-        <v>2523</v>
+        <v>2120</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1510,46 +1510,46 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0035</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0031</t>
+          <t>0.0047</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>v_photo[7]</t>
+          <t>v_photo[9]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5343</v>
+        <v>4495</v>
       </c>
       <c r="G24" t="n">
-        <v>2980</v>
+        <v>2472</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1558,46 +1558,46 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0048</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0045</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>v_photo[8]</t>
+          <t>v_photo[10]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.197</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4657</v>
+        <v>4078</v>
       </c>
       <c r="G25" t="n">
-        <v>2684</v>
+        <v>1788</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1606,46 +1606,46 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0033</t>
+          <t>0.0048</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0046</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>v_photo[9]</t>
+          <t>v_photo[11]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-0.116</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4061</v>
+        <v>3479</v>
       </c>
       <c r="G26" t="n">
-        <v>2597</v>
+        <v>1914</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1654,46 +1654,46 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0041</t>
+          <t>0.0058</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.006</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>v_photo[10]</t>
+          <t>v_photo[12]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4849</v>
+        <v>4150</v>
       </c>
       <c r="G27" t="n">
-        <v>2534</v>
+        <v>2491</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1702,46 +1702,46 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>0.0042</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>0.0037</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.0035</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>v_photo[11]</t>
+          <t>v_photo[13]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-0.149</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5247</v>
+        <v>4107</v>
       </c>
       <c r="G28" t="n">
-        <v>2530</v>
+        <v>2413</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1750,46 +1750,46 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0037</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0034</t>
+          <t>0.0044</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>v_photo[12]</t>
+          <t>v_photo[14]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>-0.191</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.277</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.078</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3906</v>
+        <v>3533</v>
       </c>
       <c r="G29" t="n">
-        <v>2615</v>
+        <v>2120</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1798,46 +1798,46 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0049</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>0.0047</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>v_photo[13]</t>
+          <t>v_photo[15]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>-0.243</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3973</v>
+        <v>3586</v>
       </c>
       <c r="G30" t="n">
-        <v>2796</v>
+        <v>2550</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1846,46 +1846,46 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>0.0049</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0031</t>
+          <t>0.0046</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>v_photo[14]</t>
+          <t>v_photo[16]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-0.103</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4025</v>
+        <v>3317</v>
       </c>
       <c r="G31" t="n">
-        <v>2336</v>
+        <v>2382</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1894,108 +1894,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0038</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0036</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>v_photo[15]</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>-0.179</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.252</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>5180</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2544</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.0035</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0.0033</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>v_photo[16]</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.014</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0.215</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>4731</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2779</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0032</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.0028</t>
+          <t>0.0045</t>
         </is>
       </c>
     </row>
